--- a/data/trans_camb/P6907S1-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P6907S1-Clase-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,14; -5,64</t>
+          <t>-21,33; -5,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,06; -0,7</t>
+          <t>-18,63; -0,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 6,83</t>
+          <t>-15,22; 6,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 18,12</t>
+          <t>-15,75; 18,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,36; -1,9</t>
+          <t>-21,53; -1,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 10,44</t>
+          <t>-13,12; 11,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 2,94</t>
+          <t>-15,48; 2,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,92; -4,11</t>
+          <t>-17,37; -3,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 6,45</t>
+          <t>-10,37; 5,58</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 150,47</t>
+          <t>-100,0; 77,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-92,01; 117,31</t>
+          <t>-95,01; 147,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 301,16</t>
+          <t>-100,0; 372,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 70,09</t>
+          <t>-100,0; 99,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,23; 209,34</t>
+          <t>-63,91; 212,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 100,89</t>
+          <t>-100,0; 57,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -16,96</t>
+          <t>-100,0; -25,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-60,86; 82,64</t>
+          <t>-61,01; 82,92</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-28,05; 2,18</t>
+          <t>-29,07; 2,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-28,2; 1,69</t>
+          <t>-28,34; 2,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-25,26; 5,63</t>
+          <t>-28,21; 5,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,82; 54,94</t>
+          <t>-14,91; 54,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,75; -2,85</t>
+          <t>-23,22; -2,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 22,37</t>
+          <t>-9,82; 24,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,1; 7,36</t>
+          <t>-17,61; 8,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,7; -3,25</t>
+          <t>-20,63; -2,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 9,38</t>
+          <t>-12,84; 10,57</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 385,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 73,08</t>
+          <t>-100,0; 160,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-87,1; 86,68</t>
+          <t>-89,31; 96,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,59; 595,5</t>
+          <t>-74,95; 665,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 130,01</t>
+          <t>-100,0; 134,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -14,09</t>
+          <t>-100,0; 9,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-69,69; 117,31</t>
+          <t>-64,87; 151,85</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 14,56</t>
+          <t>-10,42; 12,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 7,69</t>
+          <t>-10,2; 7,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 30,65</t>
+          <t>1,65; 29,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 0,0</t>
+          <t>-29,36; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-31,34; 0,0</t>
+          <t>-26,31; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 22,06</t>
+          <t>-13,08; 22,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 5,86</t>
+          <t>-12,01; 5,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 6,34</t>
+          <t>-9,55; 7,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 24,43</t>
+          <t>1,81; 25,78</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-78,25; 349,31</t>
+          <t>-100,0; 238,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,79; 153,72</t>
+          <t>-75,27; 190,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 611,89</t>
+          <t>-3,47; 504,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-86,66; 132,2</t>
+          <t>-87,3; 126,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,02; 163,33</t>
+          <t>-80,09; 155,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 485,96</t>
+          <t>3,73; 481,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 10,97</t>
+          <t>-5,0; 11,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,99; -1,28</t>
+          <t>-9,05; -1,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 7,7</t>
+          <t>-3,94; 7,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-26,75; -6,14</t>
+          <t>-25,27; -6,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-22,62; -2,73</t>
+          <t>-24,19; -3,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 3,02</t>
+          <t>-19,06; 2,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 2,6</t>
+          <t>-7,88; 3,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,31; -2,46</t>
+          <t>-9,96; -2,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 4,87</t>
+          <t>-4,61; 4,7</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-73,01; 255,65</t>
+          <t>-72,02; 299,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1,27</t>
+          <t>-100,0; -3,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,21; 196,83</t>
+          <t>-48,63; 201,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -5,85</t>
+          <t>-100,0; -4,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-82,47; 56,07</t>
+          <t>-81,67; 42,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-86,97; 71,66</t>
+          <t>-84,37; 80,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-94,58; -33,21</t>
+          <t>-94,21; -29,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-46,43; 84,89</t>
+          <t>-47,37; 88,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-21,23; -4,1</t>
+          <t>-20,77; -4,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 0,33</t>
+          <t>-18,35; 0,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 9,31</t>
+          <t>-12,48; 8,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,7; -3,07</t>
+          <t>-16,02; -2,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 9,0</t>
+          <t>-11,21; 8,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 1,03</t>
+          <t>-13,33; 1,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-15,88; -4,7</t>
+          <t>-15,39; -4,93</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 0,26</t>
+          <t>-11,96; 1,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 1,2</t>
+          <t>-11,69; 0,77</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 62,84</t>
+          <t>-100,0; 74,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-86,4; 245,4</t>
+          <t>-85,76; 264,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1667,34 +1667,34 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 352,32</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-92,17; 53,08</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-92,72; 40,46</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-90,45; 39,45</t>
+          <t>-91,82; 34,19</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-82,73; 30,6</t>
+          <t>-84,63; 23,55</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1704,47 +1704,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3,72</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5,73</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-7,89</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-8,27</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2,94</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5,3</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-6,6</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,41</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,15; 1,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,37; -2,5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,54; 6,79</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,33; -2,67</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,36; -4,09</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,49; 1,51</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,81; -1,36</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,4; -4,12</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,04; 2,9</t>
         </is>
       </c>
     </row>
@@ -1810,47 +1810,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-40,41%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-62,15%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-73,5%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-77,02%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-27,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-54,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-68,06%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-4,25%</t>
         </is>
       </c>
     </row>
@@ -1863,282 +1863,65 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-75,87; 17,28</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,47; -29,69</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-23,83; 92,94</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -19,6</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-93,2; -45,35</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-59,1; 21,8</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,5; -14,71</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-81,84; -44,51</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-34,77; 36,69</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>-3,72</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>-5,73</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1,62</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-7,89</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-8,27</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-2,94</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-5,3</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-6,6</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>-0,41</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>-7,97; 1,05</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>-9,31; -2,52</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>-2,38; 7,02</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>-12,91; -2,21</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>-13,12; -3,75</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-8,02; 2,03</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-8,94; -1,63</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-9,37; -4,08</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>-3,77; 2,93</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>-40,41%</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>-62,15%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-73,5%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-77,02%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-27,41%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-54,64%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-68,06%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>-4,25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>-74,55; 20,46</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>-80,42; -29,97</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>-22,32; 106,95</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>-92,52; -9,92</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>-93,29; -43,66</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-56,38; 27,83</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-78,78; -15,37</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>-81,76; -47,87</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>-32,62; 34,72</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A24:A27"/>

--- a/data/trans_camb/P6907S1-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P6907S1-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-4,38</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,09</t>
+          <t>-0,27</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,33; -5,53</t>
+          <t>-20,91; -5,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,63; -0,61</t>
+          <t>-17,91; -0,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 6,91</t>
+          <t>-11,61; 14,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 18,3</t>
+          <t>-15,6; 22,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,53; -1,61</t>
+          <t>-24,14; -1,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 11,15</t>
+          <t>-13,75; 10,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 2,43</t>
+          <t>-15,86; 3,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,37; -3,86</t>
+          <t>-16,96; -3,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 5,58</t>
+          <t>-8,61; 7,95</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-37,37%</t>
+          <t>-9,01%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-5,26%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-17,05%</t>
+          <t>-2,21%</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 77,61</t>
+          <t>-100,0; 235,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-95,01; 147,79</t>
+          <t>-79,47; 255,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 372,97</t>
+          <t>-100,0; 405,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 99,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,91; 212,23</t>
+          <t>-65,91; 184,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 57,48</t>
+          <t>-100,0; 87,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -25,4</t>
+          <t>-100,0; -20,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-61,01; 82,92</t>
+          <t>-53,18; 105,78</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-8,08</t>
+          <t>-8,1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,11</t>
+          <t>3,87</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,24</t>
+          <t>-2,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-29,07; 2,59</t>
+          <t>-29,29; 2,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-28,34; 2,24</t>
+          <t>-28,12; 3,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-28,21; 5,54</t>
+          <t>-27,16; 6,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 54,54</t>
+          <t>-15,32; 55,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,22; -2,45</t>
+          <t>-22,5; -2,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 24,06</t>
+          <t>-11,49; 20,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 8,75</t>
+          <t>-17,88; 7,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,63; -2,0</t>
+          <t>-21,66; -2,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 10,57</t>
+          <t>-12,37; 9,47</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-45,37%</t>
+          <t>-45,47%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-15,85%</t>
+          <t>-16,29%</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 160,85</t>
+          <t>-100,0; 156,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-89,31; 96,06</t>
+          <t>-87,34; 139,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,95; 665,42</t>
+          <t>-70,12; 587,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 134,35</t>
+          <t>-100,0; 108,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 9,69</t>
+          <t>-100,0; -2,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-64,87; 151,85</t>
+          <t>-62,91; 149,32</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14,43</t>
+          <t>14,08</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,35</t>
+          <t>3,89</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12,0</t>
+          <t>11,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 12,34</t>
+          <t>-10,44; 13,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 7,63</t>
+          <t>-10,04; 8,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 29,47</t>
+          <t>1,35; 31,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-29,36; 0,0</t>
+          <t>-28,14; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,31; 0,0</t>
+          <t>-31,28; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 22,84</t>
+          <t>-16,07; 17,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 5,22</t>
+          <t>-12,01; 6,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 7,51</t>
+          <t>-9,78; 7,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 25,78</t>
+          <t>1,14; 26,32</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151,63%</t>
+          <t>148,02%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>132,54%</t>
+          <t>123,47%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 238,12</t>
+          <t>-86,41; 318,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-75,27; 190,83</t>
+          <t>-79,63; 193,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 504,17</t>
+          <t>-8,56; 607,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-87,3; 126,91</t>
+          <t>-100,0; 190,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,09; 155,23</t>
+          <t>-76,88; 166,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,73; 481,49</t>
+          <t>-6,46; 472,33</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,71</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,58</t>
+          <t>-6,88</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>-0,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 11,95</t>
+          <t>-5,07; 10,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -1,29</t>
+          <t>-9,28; -1,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 7,79</t>
+          <t>-4,55; 5,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-25,27; -6,04</t>
+          <t>-26,56; -6,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-24,19; -3,72</t>
+          <t>-24,76; -3,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,06; 2,59</t>
+          <t>-19,59; 2,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 3,69</t>
+          <t>-8,06; 3,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-9,96; -2,49</t>
+          <t>-10,12; -2,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 4,7</t>
+          <t>-5,38; 3,89</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-46,03%</t>
+          <t>-48,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>-10,08%</t>
         </is>
       </c>
     </row>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-72,02; 299,6</t>
+          <t>-71,84; 234,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -3,6</t>
+          <t>-100,0; 6,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,63; 201,25</t>
+          <t>-58,73; 151,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1451,27 +1451,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -4,55</t>
+          <t>-100,0; 0,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,67; 42,92</t>
+          <t>-83,49; 41,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-84,37; 80,22</t>
+          <t>-85,86; 75,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-94,21; -29,33</t>
+          <t>-94,39; -33,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-47,37; 88,42</t>
+          <t>-53,47; 77,9</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,32</t>
+          <t>-3,8</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,74</t>
+          <t>-2,5</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,55</t>
+          <t>-3,25</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-20,77; -4,25</t>
+          <t>-21,52; -4,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 0,02</t>
+          <t>-17,71; 0,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 8,9</t>
+          <t>-14,93; 7,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,02; -2,91</t>
+          <t>-16,05; -2,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 8,03</t>
+          <t>-11,06; 7,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 1,16</t>
+          <t>-11,51; 3,57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-15,39; -4,93</t>
+          <t>-15,63; -4,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 1,06</t>
+          <t>-12,4; 0,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 0,77</t>
+          <t>-10,57; 1,96</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-22,95%</t>
+          <t>-37,57%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-61,5%</t>
+          <t>-32,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-51,09%</t>
+          <t>-36,55%</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 74,2</t>
+          <t>-100,0; 98,77</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-85,76; 264,65</t>
+          <t>-90,94; 197,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 352,32</t>
+          <t>-100,0; 347,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-92,17; 53,08</t>
+          <t>-78,94; 134,32</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-91,82; 34,19</t>
+          <t>-91,4; 33,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-84,63; 23,55</t>
+          <t>-75,78; 40,09</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-2,94</t>
+          <t>-1,87</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>-0,09</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 1,01</t>
+          <t>-8,19; 1,67</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,37; -2,5</t>
+          <t>-9,23; -2,09</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 6,79</t>
+          <t>-3,06; 6,27</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-13,33; -2,67</t>
+          <t>-12,88; -2,73</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-13,36; -4,09</t>
+          <t>-13,14; -3,94</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 1,51</t>
+          <t>-7,06; 2,89</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,81; -1,36</t>
+          <t>-8,22; -1,61</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-9,4; -4,12</t>
+          <t>-9,66; -4,11</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 2,9</t>
+          <t>-3,41; 3,09</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-27,41%</t>
+          <t>-17,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-4,25%</t>
+          <t>-0,95%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-75,87; 17,28</t>
+          <t>-74,98; 30,74</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-82,47; -29,69</t>
+          <t>-81,96; -27,42</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 92,94</t>
+          <t>-29,31; 88,61</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -19,6</t>
+          <t>-93,37; -20,83</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-93,2; -45,35</t>
+          <t>-92,99; -43,82</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-59,1; 21,8</t>
+          <t>-52,38; 39,4</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-77,5; -14,71</t>
+          <t>-76,33; -17,21</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-81,84; -44,51</t>
+          <t>-81,41; -46,05</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-34,77; 36,69</t>
+          <t>-31,72; 36,85</t>
         </is>
       </c>
     </row>
